--- a/양식/키워드변경_양식.xlsx
+++ b/양식/키워드변경_양식.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키워드변경" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="등록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,17 +26,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
       <color rgb="00999999"/>
       <sz val="10"/>
     </font>
@@ -50,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000277BD"/>
+        <fgColor rgb="007B1FA2"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,31 +58,28 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,88 +447,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MID는 필수, Pcode는 비우면 MID 전체 대상 / 콤마(,)로 여러 개 입력 가능(배분 기능과 함께 사용). 키워드는 쉼표(,)로 구분, A/B 동일 입력됩니다. 메모는 비우면 오늘 날짜 자동 입력. 이 예시 행은 지우고 실제 데이터로 채워서 업로드하세요.</t>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Pcode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>키워드</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Pcode</t>
-        </is>
-      </c>
+          <t>1839711962</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>키워드</t>
+          <t>귀금속,귀금속방,귀금속위치</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1839711962</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>귀금속,귀금속방,귀금속위치</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
           <t>예: MID 전체 대상, 배분 OFF면 전체 pcode에 동일 키워드</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1839711962</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>P21169CA0DAB3776F,P21169CA0DAB3776G</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>귀금속,보석,금은방</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>예: 이 두 pcode에 배분(배분 ON 시 균등분배)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/양식/키워드변경_양식.xlsx
+++ b/양식/키워드변경_양식.xlsx
@@ -35,7 +35,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007B1FA2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,22 +465,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Pcode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>키워드</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>메모</t>
         </is>

--- a/양식/키워드변경_양식.xlsx
+++ b/양식/키워드변경_양식.xlsx
@@ -455,13 +455,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -480,11 +479,6 @@
           <t>키워드</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -498,11 +492,6 @@
           <t>귀금속,귀금속방,귀금속위치</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>예: MID 전체 대상, 배분 OFF면 전체 pcode에 동일 키워드</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/양식/키워드변경_양식.xlsx
+++ b/양식/키워드변경_양식.xlsx
@@ -455,12 +455,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -479,6 +480,11 @@
           <t>키워드</t>
         </is>
       </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>유입플키워드</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -490,6 +496,11 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>귀금속,귀금속방,귀금속위치</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>강남맛집,강남맛집추천</t>
         </is>
       </c>
     </row>

--- a/양식/키워드변경_양식.xlsx
+++ b/양식/키워드변경_양식.xlsx
@@ -477,12 +477,12 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>키워드</t>
+          <t>비즈핏 키워드</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>유입플키워드</t>
+          <t>유입플 키워드</t>
         </is>
       </c>
     </row>

--- a/양식/키워드변경_양식.xlsx
+++ b/양식/키워드변경_양식.xlsx
@@ -455,10 +455,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
@@ -467,20 +467,25 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>영업점</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Pcode</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>비즈핏 키워드</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>유입플 키워드</t>
         </is>
@@ -489,16 +494,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1839711962</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
+          <t>제이솔컴퍼니</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1230085864</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>P2116A864DC2B0CF2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>귀금속,귀금속방,귀금속위치</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>강남맛집,강남맛집추천</t>
         </is>
